--- a/교통량조사_조사지점4/주도로_교통량_조사지점4.xlsx
+++ b/교통량조사_조사지점4/주도로_교통량_조사지점4.xlsx
@@ -561,37 +561,37 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="K3" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -607,31 +607,31 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="K4" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -641,37 +641,37 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="J6" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -727,31 +727,31 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -761,37 +761,37 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -841,37 +841,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -881,37 +881,37 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1266,37 +1266,37 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -1306,37 +1306,37 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -1346,37 +1346,37 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1389,19 +1389,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -1410,13 +1410,13 @@
         <v>4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -1441,22 +1441,22 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -1466,37 +1466,37 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -1518,25 +1518,25 @@
         <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -2011,37 +2011,37 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -2051,37 +2051,37 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -2091,37 +2091,37 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>19</v>
@@ -2152,16 +2152,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -2171,37 +2171,37 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>44</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -2211,37 +2211,37 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -2291,37 +2291,37 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2343,25 +2343,25 @@
         <v>1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
